--- a/artfynd/S 1180-2026 artfynd.xlsx
+++ b/artfynd/S 1180-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY292"/>
+  <dimension ref="A1:AZ292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209461</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209465</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,6 +1065,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209601</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1186,6 +1206,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79519403</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1322,6 +1347,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79519108</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1448,6 +1478,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209597</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1574,6 +1609,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209585</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1700,6 +1740,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209602</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1826,6 +1871,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209603</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1952,6 +2002,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209604</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2088,6 +2143,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79523575</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2214,6 +2274,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209528</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2350,6 +2415,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79523473</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2486,6 +2556,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79523474</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2622,6 +2697,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79523475</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2758,6 +2838,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79523476</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2894,6 +2979,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79523477</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3030,6 +3120,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79523478</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3166,6 +3261,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79523479</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3292,6 +3392,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209466</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3418,6 +3523,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209470</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3544,6 +3654,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209487</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3670,6 +3785,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209488</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3796,6 +3916,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209492</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3922,6 +4047,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209497</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4048,6 +4178,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209510</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4174,6 +4309,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209520</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4300,6 +4440,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209547</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4426,6 +4571,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209578</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4552,6 +4702,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209589</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4678,6 +4833,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209590</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4804,6 +4964,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209592</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4930,6 +5095,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209598</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5056,6 +5226,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209600</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5182,6 +5357,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209605</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5318,6 +5498,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79519992</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5454,6 +5639,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79519993</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5590,6 +5780,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79519994</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5726,6 +5921,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79519995</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5862,6 +6062,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79519997</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5998,6 +6203,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79519998</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6134,6 +6344,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79519999</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6270,6 +6485,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520000</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6406,6 +6626,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520001</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6542,6 +6767,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520002</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6678,6 +6908,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520004</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6814,6 +7049,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520005</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6950,6 +7190,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520006</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7086,6 +7331,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520007</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7222,6 +7472,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520008</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7358,6 +7613,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520009</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7494,6 +7754,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520010</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7630,6 +7895,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520011</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7766,6 +8036,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520012</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7902,6 +8177,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520013</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -8038,6 +8318,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520014</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8174,6 +8459,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520015</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8310,6 +8600,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520016</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8446,6 +8741,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520032</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8582,6 +8882,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520034</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8718,6 +9023,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520036</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8854,6 +9164,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520038</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8990,6 +9305,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520040</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -9126,6 +9446,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520042</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -9262,6 +9587,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520044</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -9398,6 +9728,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520045</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -9534,6 +9869,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520046</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -9670,6 +10010,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520047</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9806,6 +10151,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520048</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9942,6 +10292,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520049</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -10078,6 +10433,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520051</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -10214,6 +10574,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520052</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -10350,6 +10715,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520054</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -10486,6 +10856,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520055</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -10622,6 +10997,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520057</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -10758,6 +11138,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520059</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -10894,6 +11279,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520060</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -11030,6 +11420,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520061</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -11166,6 +11561,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520062</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -11302,6 +11702,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520063</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -11438,6 +11843,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520064</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -11574,6 +11984,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520065</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -11710,6 +12125,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520066</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -11846,6 +12266,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520067</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -11972,6 +12397,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209496</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -12108,6 +12538,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520069</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -12244,6 +12679,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520070</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -12380,6 +12820,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520071</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -12516,6 +12961,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520112</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -12652,6 +13102,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520113</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -12788,6 +13243,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520114</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -12924,6 +13384,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520115</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -13060,6 +13525,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520116</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -13196,6 +13666,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520119</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -13332,6 +13807,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520120</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -13468,6 +13948,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520121</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -13604,6 +14089,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520122</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -13740,6 +14230,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520123</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -13876,6 +14371,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520124</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -14012,6 +14512,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520125</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -14148,6 +14653,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520126</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -14284,6 +14794,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520127</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -14420,6 +14935,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520128</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -14556,6 +15076,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520129</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -14692,6 +15217,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520130</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -14828,6 +15358,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520131</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -14964,6 +15499,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520132</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -15100,6 +15640,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520133</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -15236,6 +15781,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520134</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -15372,6 +15922,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520135</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -15508,6 +16063,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520137</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -15644,6 +16204,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520138</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -15780,6 +16345,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520139</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -15916,6 +16486,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520140</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -16042,6 +16617,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209459</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -16168,6 +16748,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209460</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -16294,6 +16879,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209462</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -16420,6 +17010,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209463</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -16546,6 +17141,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209464</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -16672,6 +17272,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209467</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -16798,6 +17403,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209468</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -16924,6 +17534,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209469</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -17050,6 +17665,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209472</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -17176,6 +17796,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209476</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -17302,6 +17927,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209477</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -17428,6 +18058,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209478</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -17554,6 +18189,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209479</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -17680,6 +18320,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209480</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -17806,6 +18451,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209482</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -17932,6 +18582,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209483</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -18058,6 +18713,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209485</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -18184,6 +18844,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209486</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -18310,6 +18975,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209489</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -18436,6 +19106,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209490</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -18562,6 +19237,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209493</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -18688,6 +19368,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209501</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -18814,6 +19499,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209502</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -18940,6 +19630,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209505</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -19066,6 +19761,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209507</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -19192,6 +19892,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209512</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -19318,6 +20023,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209515</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -19444,6 +20154,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209519</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -19570,6 +20285,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209523</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -19696,6 +20416,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209525</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -19822,6 +20547,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209530</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -19948,6 +20678,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209532</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -20074,6 +20809,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209535</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -20200,6 +20940,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209537</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -20326,6 +21071,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209538</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -20452,6 +21202,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209539</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -20578,6 +21333,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209544</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -20704,6 +21464,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209548</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -20830,6 +21595,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209551</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -20956,6 +21726,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209553</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -21082,6 +21857,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209556</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -21208,6 +21988,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209558</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -21334,6 +22119,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209559</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -21460,6 +22250,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209560</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -21586,6 +22381,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209562</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -21712,6 +22512,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209564</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -21838,6 +22643,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209566</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -21964,6 +22774,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209567</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -22090,6 +22905,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209568</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -22216,6 +23036,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209569</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -22342,6 +23167,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209570</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -22468,6 +23298,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209575</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -22594,6 +23429,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209577</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -22720,6 +23560,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209579</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -22846,6 +23691,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209580</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -22972,6 +23822,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209581</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -23098,6 +23953,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209595</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -23229,6 +24089,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209805</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -23365,6 +24230,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522609</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -23501,6 +24371,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522610</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -23637,6 +24512,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522611</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -23773,6 +24653,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522612</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -23909,6 +24794,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522613</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -24045,6 +24935,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522674</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -24181,6 +25076,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522675</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -24317,6 +25217,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522676</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -24453,6 +25358,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522677</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -24589,6 +25499,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522679</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -24725,6 +25640,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522680</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -24861,6 +25781,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522681</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -24997,6 +25922,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522682</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -25133,6 +26063,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522683</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -25269,6 +26204,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522684</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -25405,6 +26345,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522685</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -25541,6 +26486,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522686</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -25677,6 +26627,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522687</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -25813,6 +26768,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522688</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -25949,6 +26909,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522689</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -26085,6 +27050,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522690</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -26221,6 +27191,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522691</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -26357,6 +27332,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522692</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -26493,6 +27473,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522693</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -26629,6 +27614,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522694</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -26765,6 +27755,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522695</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -26901,6 +27896,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522696</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -27037,6 +28037,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522697</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -27173,6 +28178,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522698</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -27309,6 +28319,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522699</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -27445,6 +28460,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522700</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -27581,6 +28601,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522701</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -27717,6 +28742,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522702</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -27853,6 +28883,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522703</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -27989,6 +29024,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522704</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -28125,6 +29165,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522705</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -28261,6 +29306,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522706</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -28397,6 +29447,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522707</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -28533,6 +29588,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522708</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -28669,6 +29729,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522709</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -28805,6 +29870,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522710</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -28941,6 +30011,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522711</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -29077,6 +30152,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522712</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -29213,6 +30293,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522713</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -29349,6 +30434,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522715</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -29485,6 +30575,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522716</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -29621,6 +30716,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522717</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -29757,6 +30857,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522718</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -29893,6 +30998,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522719</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -30029,6 +31139,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522720</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -30165,6 +31280,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522721</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -30301,6 +31421,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522724</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -30437,6 +31562,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522725</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -30573,6 +31703,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522797</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -30699,6 +31834,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209542</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -30825,6 +31965,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209591</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -30932,6 +32077,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62416542</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -31068,6 +32218,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522922</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -31204,6 +32359,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522923</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -31340,6 +32500,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78505889</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -31476,6 +32641,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78505890</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -31612,6 +32782,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78505891</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -31748,6 +32923,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79519041</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -31884,6 +33064,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79519042</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -32020,6 +33205,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79519043</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -32146,6 +33336,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209471</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -32272,6 +33467,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209473</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -32398,6 +33598,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209474</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -32524,6 +33729,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209481</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -32650,6 +33860,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209484</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -32776,6 +33991,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209491</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -32902,6 +34122,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209495</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -33028,6 +34253,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209498</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -33154,6 +34384,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209500</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -33280,6 +34515,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209503</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -33406,6 +34646,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209504</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -33532,6 +34777,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209506</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -33658,6 +34908,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209508</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -33784,6 +35039,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209509</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -33910,6 +35170,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209511</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -34036,6 +35301,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209513</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -34162,6 +35432,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209514</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -34288,6 +35563,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209516</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -34414,6 +35694,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209517</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -34540,6 +35825,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209518</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -34666,6 +35956,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209521</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -34792,6 +36087,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209522</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -34918,6 +36218,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209524</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -35044,6 +36349,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209526</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -35170,6 +36480,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209527</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -35296,6 +36611,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209529</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -35422,6 +36742,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209533</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -35548,6 +36873,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209534</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -35674,6 +37004,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209536</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -35800,6 +37135,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209540</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -35926,6 +37266,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209541</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -36052,6 +37397,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209543</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -36178,6 +37528,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209545</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -36304,6 +37659,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209546</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -36430,6 +37790,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209549</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -36556,6 +37921,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209550</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -36682,6 +38052,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209552</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -36808,6 +38183,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209555</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -36934,6 +38314,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209557</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -37060,6 +38445,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209561</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -37186,6 +38576,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209563</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -37312,6 +38707,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209565</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -37438,6 +38838,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209571</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -37564,6 +38969,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209572</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -37690,6 +39100,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209573</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -37816,6 +39231,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209574</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -37942,6 +39362,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209576</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -38068,6 +39493,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209582</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -38194,6 +39624,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209584</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -38320,6 +39755,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209586</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -38446,6 +39886,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209587</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -38572,6 +40017,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209599</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -38708,6 +40158,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79523124</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -38834,8 +40289,306 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209593</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>